--- a/AOL.xlsx
+++ b/AOL.xlsx
@@ -12,130 +12,91 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10044"/>
   </bookViews>
   <sheets>
-    <sheet name="ATG" sheetId="1" r:id="rId1"/>
+    <sheet name="AO" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
-  <si>
-    <t>lakk</t>
-  </si>
-  <si>
-    <t>maqaa</t>
-  </si>
-  <si>
-    <t>guyyaa_buusi</t>
-  </si>
-  <si>
-    <t>buusii_jiaa</t>
-  </si>
-  <si>
-    <t>buusii_dabalataa</t>
-  </si>
-  <si>
-    <t>guyyaa_xummuraa</t>
-  </si>
-  <si>
-    <t>amma_adabbii</t>
-  </si>
-  <si>
-    <t>Abarraa Miidhaksaa</t>
-  </si>
-  <si>
-    <t>Abdiisaa Leellisaa</t>
-  </si>
-  <si>
-    <t>Addisuu Bokii</t>
-  </si>
-  <si>
-    <t>Ajjamaa Gurmeessaa</t>
-  </si>
-  <si>
-    <t>Alam Suphaa</t>
-  </si>
-  <si>
-    <t>Alamuu Nagaash</t>
-  </si>
-  <si>
-    <t>Baqqalaa Guddisaa</t>
-  </si>
-  <si>
-    <t>Biraanuu Namarraa</t>
-  </si>
-  <si>
-    <t>Dajanee Caalaa</t>
-  </si>
-  <si>
-    <t>Dajanee Xaafaa</t>
-  </si>
-  <si>
-    <t>Dibaabaa Dheeressaa</t>
-  </si>
-  <si>
-    <t>Dirribaa Taammiruu</t>
-  </si>
-  <si>
-    <t>Fayyisaa Baayisaa</t>
-  </si>
-  <si>
-    <t>Fayyisaa Badhuu</t>
-  </si>
-  <si>
-    <t>Fayyisaa Dhiyeessaa</t>
-  </si>
-  <si>
-    <t>Fayyisaa Naggasaa</t>
-  </si>
-  <si>
-    <t>Girmaa Badhuu</t>
-  </si>
-  <si>
-    <t>NULL</t>
-  </si>
-  <si>
-    <t>Girmaa Hayiluu</t>
-  </si>
-  <si>
-    <t>Girmaa Xaafaa</t>
-  </si>
-  <si>
-    <t>Hayiluu Taraaraa</t>
-  </si>
-  <si>
-    <t>Jaalannee Fayyisaa</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
+  <si>
+    <t>business_date</t>
+  </si>
+  <si>
+    <t>Id_no</t>
+  </si>
+  <si>
+    <t>Full_name</t>
+  </si>
+  <si>
+    <t>Phone_no</t>
+  </si>
+  <si>
+    <t>Monthly_payment</t>
+  </si>
+  <si>
+    <t>Additional_payment</t>
+  </si>
+  <si>
+    <t>Total_payment</t>
+  </si>
+  <si>
+    <t>loan</t>
+  </si>
+  <si>
+    <t>Xajituu Gaddisaa</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Baqalaa Tolasaa</t>
+  </si>
+  <si>
+    <t>Barsiisaa Margaa</t>
+  </si>
+  <si>
+    <t>Dasalanyi Ababaa</t>
+  </si>
+  <si>
+    <t>Fayisaa Badhuu</t>
+  </si>
+  <si>
+    <t>Getuu Baqalaa</t>
+  </si>
+  <si>
+    <t>Girmaa Masqalaa</t>
+  </si>
+  <si>
+    <t>Girmaa Qorichoo</t>
+  </si>
+  <si>
+    <t>Gizahu Hayiluu</t>
   </si>
   <si>
     <t>Jabeessaa Caalaa</t>
   </si>
   <si>
-    <t>Kaasuu Margaa</t>
-  </si>
-  <si>
-    <t>Kabbabaa Dheeressaa</t>
-  </si>
-  <si>
-    <t>Katamaa Kabbee</t>
-  </si>
-  <si>
     <t>Lammii Diroo</t>
   </si>
   <si>
-    <t>Mootummaa Balaayi</t>
-  </si>
-  <si>
-    <t>Taddasaa Dabalaa</t>
-  </si>
-  <si>
-    <t>Tashoomaa Abarraa</t>
+    <t>Mangee Lammaa</t>
   </si>
   <si>
     <t>Walfaanaa Magarsaa</t>
   </si>
   <si>
-    <t>Wandimmuu Adaanaa</t>
+    <t>Xahayi Hayilee</t>
+  </si>
+  <si>
+    <t>Baayisaa Diribaa</t>
+  </si>
+  <si>
+    <t>Calchisaa Tarafaa</t>
+  </si>
+  <si>
+    <t>Getuu Lataa</t>
   </si>
 </sst>
 </file>
@@ -943,19 +904,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -977,717 +939,449 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1001</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1">
-        <v>46215</v>
-      </c>
-      <c r="D2">
-        <v>200</v>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>46216</v>
+      </c>
+      <c r="B2">
+        <v>101</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
       </c>
       <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2" s="1">
-        <v>46215</v>
+        <v>6600</v>
+      </c>
+      <c r="F2">
+        <v>2000</v>
       </c>
       <c r="G2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>1002</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="1">
-        <v>46215</v>
+        <v>8600</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>46216</v>
+      </c>
+      <c r="B3">
+        <v>102</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
       </c>
       <c r="D3">
-        <v>200</v>
+        <v>928276274</v>
       </c>
       <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3" s="1">
-        <v>46215</v>
+        <v>6700</v>
+      </c>
+      <c r="F3">
+        <v>2000</v>
       </c>
       <c r="G3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>1003</v>
-      </c>
-      <c r="B4" t="s">
+        <v>8700</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>46216</v>
+      </c>
+      <c r="B4">
+        <v>103</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4">
+        <v>930308503</v>
+      </c>
+      <c r="E4">
+        <v>6500</v>
+      </c>
+      <c r="F4">
+        <v>2000</v>
+      </c>
+      <c r="G4">
+        <v>8500</v>
+      </c>
+      <c r="H4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>46216</v>
+      </c>
+      <c r="B5">
+        <v>104</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="1">
-        <v>46215</v>
-      </c>
-      <c r="D4">
-        <v>200</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4" s="1">
-        <v>46215</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>1004</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="1">
-        <v>46215</v>
-      </c>
-      <c r="D5">
-        <v>200</v>
-      </c>
       <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5" s="1">
-        <v>46215</v>
+        <v>800</v>
+      </c>
+      <c r="F5">
+        <v>500</v>
       </c>
       <c r="G5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>1005</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="1">
-        <v>46215</v>
+        <v>1300</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>46216</v>
+      </c>
+      <c r="B6">
+        <v>105</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
       </c>
       <c r="D6">
-        <v>200</v>
+        <v>977677737</v>
       </c>
       <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6" s="1">
-        <v>46215</v>
+        <v>6500</v>
+      </c>
+      <c r="F6">
+        <v>2000</v>
       </c>
       <c r="G6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>1006</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="1">
-        <v>46215</v>
+        <v>8500</v>
+      </c>
+      <c r="H6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>46216</v>
+      </c>
+      <c r="B7">
+        <v>106</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
       </c>
       <c r="D7">
-        <v>200</v>
+        <v>912672957</v>
       </c>
       <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1">
-        <v>46215</v>
+        <v>6500</v>
+      </c>
+      <c r="F7">
+        <v>2000</v>
       </c>
       <c r="G7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>1007</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="1">
-        <v>46215</v>
+        <v>8500</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>46216</v>
+      </c>
+      <c r="B8">
+        <v>107</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
       </c>
       <c r="D8">
-        <v>200</v>
+        <v>913354650</v>
       </c>
       <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1">
-        <v>46215</v>
+        <v>6500</v>
+      </c>
+      <c r="F8">
+        <v>2000</v>
       </c>
       <c r="G8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>1008</v>
-      </c>
-      <c r="B9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="1">
-        <v>46215</v>
+        <v>8500</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>46216</v>
+      </c>
+      <c r="B9">
+        <v>108</v>
+      </c>
+      <c r="C9" t="s">
+        <v>16</v>
       </c>
       <c r="D9">
-        <v>200</v>
+        <v>920116666</v>
       </c>
       <c r="E9">
-        <v>1800</v>
-      </c>
-      <c r="F9" s="1">
-        <v>46215</v>
+        <v>6500</v>
+      </c>
+      <c r="F9">
+        <v>2000</v>
       </c>
       <c r="G9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>1009</v>
-      </c>
-      <c r="B10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="1">
-        <v>46215</v>
+        <v>8500</v>
+      </c>
+      <c r="H9">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>46216</v>
+      </c>
+      <c r="B10">
+        <v>109</v>
+      </c>
+      <c r="C10" t="s">
+        <v>17</v>
       </c>
       <c r="D10">
-        <v>200</v>
+        <v>912609998</v>
       </c>
       <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10" s="1">
-        <v>46215</v>
+        <v>6600</v>
+      </c>
+      <c r="F10">
+        <v>2000</v>
       </c>
       <c r="G10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>10010</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="1">
-        <v>46215</v>
+        <v>8600</v>
+      </c>
+      <c r="H10">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>46216</v>
+      </c>
+      <c r="B11">
+        <v>1010</v>
+      </c>
+      <c r="C11" t="s">
+        <v>18</v>
       </c>
       <c r="D11">
-        <v>200</v>
+        <v>912695064</v>
       </c>
       <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11" s="1">
-        <v>46215</v>
+        <v>6500</v>
+      </c>
+      <c r="F11">
+        <v>2000</v>
       </c>
       <c r="G11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>10011</v>
-      </c>
-      <c r="B12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="1">
-        <v>46215</v>
+        <v>8500</v>
+      </c>
+      <c r="H11">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>46216</v>
+      </c>
+      <c r="B12">
+        <v>1011</v>
+      </c>
+      <c r="C12" t="s">
+        <v>19</v>
       </c>
       <c r="D12">
-        <v>200</v>
+        <v>922956646</v>
       </c>
       <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12" s="1">
-        <v>46215</v>
+        <v>6500</v>
+      </c>
+      <c r="F12">
+        <v>2000</v>
       </c>
       <c r="G12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>10012</v>
-      </c>
-      <c r="B13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="1">
-        <v>46215</v>
+        <v>8500</v>
+      </c>
+      <c r="H12">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>46216</v>
+      </c>
+      <c r="B13">
+        <v>1012</v>
+      </c>
+      <c r="C13" t="s">
+        <v>20</v>
       </c>
       <c r="D13">
-        <v>200</v>
+        <v>919408998</v>
       </c>
       <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13" s="1">
-        <v>46215</v>
+        <v>6500</v>
+      </c>
+      <c r="F13">
+        <v>2000</v>
       </c>
       <c r="G13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>10013</v>
-      </c>
-      <c r="B14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="1">
-        <v>46215</v>
+        <v>8500</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>46216</v>
+      </c>
+      <c r="B14">
+        <v>1013</v>
+      </c>
+      <c r="C14" t="s">
+        <v>21</v>
       </c>
       <c r="D14">
-        <v>200</v>
+        <v>912861288</v>
       </c>
       <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14" s="1">
-        <v>46215</v>
+        <v>6500</v>
+      </c>
+      <c r="F14">
+        <v>2000</v>
       </c>
       <c r="G14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>10014</v>
-      </c>
-      <c r="B15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="1">
-        <v>46215</v>
+        <v>8500</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>46216</v>
+      </c>
+      <c r="B15">
+        <v>1014</v>
+      </c>
+      <c r="C15" t="s">
+        <v>22</v>
       </c>
       <c r="D15">
-        <v>200</v>
+        <v>910126329</v>
       </c>
       <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15" s="1">
-        <v>46215</v>
+        <v>500</v>
+      </c>
+      <c r="F15">
+        <v>500</v>
       </c>
       <c r="G15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>10015</v>
-      </c>
-      <c r="B16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="1">
-        <v>46215</v>
+        <v>1000</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>46216</v>
+      </c>
+      <c r="B16">
+        <v>1015</v>
+      </c>
+      <c r="C16" t="s">
+        <v>23</v>
       </c>
       <c r="D16">
-        <v>200</v>
+        <v>917307048</v>
       </c>
       <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16" s="1">
-        <v>46215</v>
+        <v>1300</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
       </c>
       <c r="G16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>10016</v>
-      </c>
-      <c r="B17" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" s="1">
-        <v>46215</v>
-      </c>
-      <c r="D17">
-        <v>200</v>
+        <v>1300</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>46216</v>
+      </c>
+      <c r="B17">
+        <v>1016</v>
+      </c>
+      <c r="C17" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" t="s">
+        <v>9</v>
       </c>
       <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17" s="1">
-        <v>46215</v>
+        <v>700</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
       </c>
       <c r="G17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>10017</v>
-      </c>
-      <c r="B18" t="s">
-        <v>23</v>
+        <v>700</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>46216</v>
+      </c>
+      <c r="B18">
+        <v>1017</v>
       </c>
       <c r="C18" t="s">
-        <v>24</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="D18" t="s">
+        <v>9</v>
       </c>
       <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18" s="1">
-        <v>46215</v>
+        <v>1000</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
       </c>
       <c r="G18">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>10018</v>
-      </c>
-      <c r="B19" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="1">
-        <v>46215</v>
-      </c>
-      <c r="D19">
-        <v>200</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19" s="1">
-        <v>46215</v>
-      </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>10019</v>
-      </c>
-      <c r="B20" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" s="1">
-        <v>46215</v>
-      </c>
-      <c r="D20">
-        <v>200</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20" s="1">
-        <v>46215</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>10020</v>
-      </c>
-      <c r="B21" t="s">
-        <v>27</v>
-      </c>
-      <c r="C21" s="1">
-        <v>46215</v>
-      </c>
-      <c r="D21">
-        <v>200</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21" s="1">
-        <v>46215</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <v>10021</v>
-      </c>
-      <c r="B22" t="s">
-        <v>28</v>
-      </c>
-      <c r="C22" s="1">
-        <v>46215</v>
-      </c>
-      <c r="D22">
-        <v>200</v>
-      </c>
-      <c r="E22">
-        <v>17400</v>
-      </c>
-      <c r="F22" s="1">
-        <v>46215</v>
-      </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <v>10022</v>
-      </c>
-      <c r="B23" t="s">
-        <v>29</v>
-      </c>
-      <c r="C23" s="1">
-        <v>46215</v>
-      </c>
-      <c r="D23">
-        <v>200</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23" s="1">
-        <v>46215</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <v>10023</v>
-      </c>
-      <c r="B24" t="s">
-        <v>30</v>
-      </c>
-      <c r="C24" s="1">
-        <v>46215</v>
-      </c>
-      <c r="D24">
-        <v>200</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-      <c r="F24" s="1">
-        <v>46215</v>
-      </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25">
-        <v>10024</v>
-      </c>
-      <c r="B25" t="s">
-        <v>31</v>
-      </c>
-      <c r="C25" t="s">
-        <v>24</v>
-      </c>
-      <c r="D25">
-        <v>0</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25" s="1">
-        <v>46215</v>
-      </c>
-      <c r="G25">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26">
-        <v>10025</v>
-      </c>
-      <c r="B26" t="s">
-        <v>32</v>
-      </c>
-      <c r="C26" s="1">
-        <v>46215</v>
-      </c>
-      <c r="D26">
-        <v>200</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26" s="1">
-        <v>46215</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27">
-        <v>10026</v>
-      </c>
-      <c r="B27" t="s">
-        <v>33</v>
-      </c>
-      <c r="C27" s="1">
-        <v>46215</v>
-      </c>
-      <c r="D27">
-        <v>200</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-      <c r="F27" s="1">
-        <v>46215</v>
-      </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28">
-        <v>10027</v>
-      </c>
-      <c r="B28" t="s">
-        <v>34</v>
-      </c>
-      <c r="C28" s="1">
-        <v>46215</v>
-      </c>
-      <c r="D28">
-        <v>200</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-      <c r="F28" s="1">
-        <v>46215</v>
-      </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29">
-        <v>10028</v>
-      </c>
-      <c r="B29" t="s">
-        <v>35</v>
-      </c>
-      <c r="C29" s="1">
-        <v>46215</v>
-      </c>
-      <c r="D29">
-        <v>200</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-      <c r="F29" s="1">
-        <v>46215</v>
-      </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30">
-        <v>10029</v>
-      </c>
-      <c r="B30" t="s">
-        <v>36</v>
-      </c>
-      <c r="C30" s="1">
-        <v>46215</v>
-      </c>
-      <c r="D30">
-        <v>200</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-      <c r="F30" s="1">
-        <v>46215</v>
-      </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31">
-        <v>10030</v>
-      </c>
-      <c r="B31" t="s">
-        <v>37</v>
-      </c>
-      <c r="C31" s="1">
-        <v>46215</v>
-      </c>
-      <c r="D31">
-        <v>200</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-      <c r="F31" s="1">
-        <v>46215</v>
-      </c>
-      <c r="G31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32">
-        <v>10031</v>
-      </c>
-      <c r="B32" t="s">
-        <v>38</v>
-      </c>
-      <c r="C32" s="1">
-        <v>46215</v>
-      </c>
-      <c r="D32">
-        <v>200</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-      <c r="F32" s="1">
-        <v>46215</v>
-      </c>
-      <c r="G32">
+        <v>1000</v>
+      </c>
+      <c r="H18">
         <v>0</v>
       </c>
     </row>
